--- a/pages/shp/uploads/24-11-2025 - 26-11-2025.xlsx
+++ b/pages/shp/uploads/24-11-2025 - 26-11-2025.xlsx
@@ -1,34 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 DATA SRI\EKSPORT\Laporan Penjualan\2025\11. NOVEMBER\upload\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="HEADER" r:id="rId3" sheetId="1"/>
-    <sheet name="ENTITAS" r:id="rId4" sheetId="2"/>
-    <sheet name="DOKUMEN" r:id="rId5" sheetId="3"/>
-    <sheet name="PENGANGKUT" r:id="rId6" sheetId="4"/>
-    <sheet name="KEMASAN" r:id="rId7" sheetId="5"/>
-    <sheet name="KONTAINER" r:id="rId8" sheetId="6"/>
-    <sheet name="KOMPONENBIAYA" r:id="rId9" sheetId="7"/>
-    <sheet name="BARANG" r:id="rId10" sheetId="8"/>
-    <sheet name="BARANGTARIF" r:id="rId11" sheetId="9"/>
-    <sheet name="BARANGDOKUMEN" r:id="rId12" sheetId="10"/>
-    <sheet name="BARANGENTITAS" r:id="rId13" sheetId="11"/>
-    <sheet name="BARANGSPEKKHUSUS" r:id="rId14" sheetId="12"/>
-    <sheet name="BARANGVD" r:id="rId15" sheetId="13"/>
-    <sheet name="BAHANBAKU" r:id="rId16" sheetId="14"/>
-    <sheet name="BAHANBAKUTARIF" r:id="rId17" sheetId="15"/>
-    <sheet name="BAHANBAKUDOKUMEN" r:id="rId18" sheetId="16"/>
-    <sheet name="PUNGUTAN" r:id="rId19" sheetId="17"/>
-    <sheet name="JAMINAN" r:id="rId20" sheetId="18"/>
-    <sheet name="BANKDEVISA" r:id="rId21" sheetId="19"/>
-    <sheet name="VERSI" r:id="rId22" sheetId="20"/>
-    <sheet name="RESPON" r:id="rId23" sheetId="21"/>
+    <sheet name="HEADER" sheetId="1" r:id="rId1"/>
+    <sheet name="ENTITAS" sheetId="2" r:id="rId2"/>
+    <sheet name="DOKUMEN" sheetId="3" r:id="rId3"/>
+    <sheet name="PENGANGKUT" sheetId="4" r:id="rId4"/>
+    <sheet name="KEMASAN" sheetId="5" r:id="rId5"/>
+    <sheet name="KONTAINER" sheetId="6" r:id="rId6"/>
+    <sheet name="KOMPONENBIAYA" sheetId="7" r:id="rId7"/>
+    <sheet name="BARANG" sheetId="8" r:id="rId8"/>
+    <sheet name="BARANGTARIF" sheetId="9" r:id="rId9"/>
+    <sheet name="BARANGDOKUMEN" sheetId="10" r:id="rId10"/>
+    <sheet name="BARANGENTITAS" sheetId="11" r:id="rId11"/>
+    <sheet name="BARANGSPEKKHUSUS" sheetId="12" r:id="rId12"/>
+    <sheet name="BARANGVD" sheetId="13" r:id="rId13"/>
+    <sheet name="BAHANBAKU" sheetId="14" r:id="rId14"/>
+    <sheet name="BAHANBAKUTARIF" sheetId="15" r:id="rId15"/>
+    <sheet name="BAHANBAKUDOKUMEN" sheetId="16" r:id="rId16"/>
+    <sheet name="PUNGUTAN" sheetId="17" r:id="rId17"/>
+    <sheet name="JAMINAN" sheetId="18" r:id="rId18"/>
+    <sheet name="BANKDEVISA" sheetId="19" r:id="rId19"/>
+    <sheet name="VERSI" sheetId="20" r:id="rId20"/>
+    <sheet name="RESPON" sheetId="21" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1569,19 +1575,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd-MM-yyyy HH:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.00"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.00"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -1606,126 +1613,388 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:DC12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="93" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:107" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2048,7 +2317,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -2109,56 +2378,56 @@
       <c r="BJ2" t="s">
         <v>119</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>540.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1380.0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>77.225</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>69.425</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>540</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>1380</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>16738</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
+        <v>77.224999999999994</v>
+      </c>
+      <c r="CC2">
+        <v>69.424999999999997</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
       </c>
       <c r="CE2" t="s">
         <v>120</v>
@@ -2187,8 +2456,8 @@
       <c r="CQ2" t="s">
         <v>117</v>
       </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
+      <c r="CT2">
+        <v>0</v>
       </c>
       <c r="CZ2" t="s">
         <v>126</v>
@@ -2197,7 +2466,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -2261,56 +2530,56 @@
       <c r="BJ3" t="s">
         <v>119</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BK3">
         <v>0.01</v>
       </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO3" t="n">
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
         <v>0.01</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BP3">
         <v>0.26</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0.038</v>
+      <c r="BQ3">
+        <v>4</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>16705</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="CC3">
+        <v>2</v>
+      </c>
+      <c r="CD3">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE3" t="s">
         <v>120</v>
@@ -2339,11 +2608,11 @@
       <c r="CQ3" t="s">
         <v>135</v>
       </c>
-      <c r="CT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0.0</v>
+      <c r="CT3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
       </c>
       <c r="CZ3" t="s">
         <v>126</v>
@@ -2352,7 +2621,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -2413,56 +2682,56 @@
       <c r="BJ4" t="s">
         <v>119</v>
       </c>
-      <c r="BK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN4" t="n">
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
         <v>251.1</v>
       </c>
-      <c r="BO4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>613.8</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB4" t="n">
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>613.79999999999995</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>16705</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
         <v>28.31</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CC4">
         <v>25.81</v>
       </c>
-      <c r="CD4" t="n">
-        <v>0.0</v>
+      <c r="CD4">
+        <v>0</v>
       </c>
       <c r="CE4" t="s">
         <v>120</v>
@@ -2491,8 +2760,8 @@
       <c r="CQ4" t="s">
         <v>141</v>
       </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
+      <c r="CT4">
+        <v>0</v>
       </c>
       <c r="CZ4" t="s">
         <v>126</v>
@@ -2501,7 +2770,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -2577,56 +2846,56 @@
       <c r="BJ5" t="s">
         <v>119</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BK5">
         <v>0.01</v>
       </c>
-      <c r="BL5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO5" t="n">
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
         <v>0.01</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BP5">
         <v>0.5</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB5" t="n">
+      <c r="BQ5">
+        <v>6</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>16705</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
         <v>3.2</v>
       </c>
-      <c r="CC5" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0.038</v>
+      <c r="CC5">
+        <v>3</v>
+      </c>
+      <c r="CD5">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE5" t="s">
         <v>120</v>
@@ -2655,11 +2924,11 @@
       <c r="CQ5" t="s">
         <v>135</v>
       </c>
-      <c r="CT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0.0</v>
+      <c r="CT5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>0</v>
       </c>
       <c r="CZ5" t="s">
         <v>126</v>
@@ -2668,7 +2937,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
@@ -2732,56 +3001,56 @@
       <c r="BJ6" t="s">
         <v>119</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BK6">
         <v>0.01</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO6" t="n">
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
         <v>0.01</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BP6">
         <v>0.48</v>
       </c>
-      <c r="BQ6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB6" t="n">
+      <c r="BQ6">
+        <v>4</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>16705</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
         <v>2.5</v>
       </c>
-      <c r="CC6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0.038</v>
+      <c r="CC6">
+        <v>2</v>
+      </c>
+      <c r="CD6">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE6" t="s">
         <v>120</v>
@@ -2810,11 +3079,11 @@
       <c r="CQ6" t="s">
         <v>141</v>
       </c>
-      <c r="CT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0.0</v>
+      <c r="CT6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
       </c>
       <c r="CZ6" t="s">
         <v>126</v>
@@ -2823,7 +3092,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
@@ -2887,55 +3156,55 @@
       <c r="BJ7" t="s">
         <v>119</v>
       </c>
-      <c r="BK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
         <v>70597.61</v>
       </c>
-      <c r="BO7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ7" t="n">
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
         <v>142292.54</v>
       </c>
-      <c r="BR7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU7" t="n">
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
         <v>142292.54</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB7" t="n">
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>16705</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
         <v>6840.69</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CC7">
         <v>6286.26</v>
       </c>
-      <c r="CD7" t="n">
+      <c r="CD7">
         <v>2.08</v>
       </c>
       <c r="CE7" t="s">
@@ -2965,11 +3234,11 @@
       <c r="CQ7" t="s">
         <v>135</v>
       </c>
-      <c r="CT7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0.0</v>
+      <c r="CT7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
       </c>
       <c r="CZ7" t="s">
         <v>126</v>
@@ -2978,7 +3247,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>157</v>
       </c>
@@ -3039,56 +3308,56 @@
       <c r="BJ8" t="s">
         <v>119</v>
       </c>
-      <c r="BK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN8" t="n">
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
         <v>2806.65</v>
       </c>
-      <c r="BO8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ8" t="n">
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
         <v>7033.95</v>
       </c>
-      <c r="BR8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>300.96</v>
-      </c>
-      <c r="CC8" t="n">
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>16705</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8">
+        <v>300.95999999999998</v>
+      </c>
+      <c r="CC8">
         <v>278.31</v>
       </c>
-      <c r="CD8" t="n">
-        <v>0.0</v>
+      <c r="CD8">
+        <v>0</v>
       </c>
       <c r="CE8" t="s">
         <v>120</v>
@@ -3117,8 +3386,8 @@
       <c r="CQ8" t="s">
         <v>141</v>
       </c>
-      <c r="CT8" t="n">
-        <v>0.0</v>
+      <c r="CT8">
+        <v>0</v>
       </c>
       <c r="CZ8" t="s">
         <v>126</v>
@@ -3127,7 +3396,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
@@ -3188,56 +3457,56 @@
       <c r="BJ9" t="s">
         <v>119</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN9" t="n">
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
         <v>835.92</v>
       </c>
-      <c r="BO9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ9" t="n">
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
         <v>2043.36</v>
       </c>
-      <c r="BR9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB9" t="n">
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>16705</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9">
         <v>94.88</v>
       </c>
-      <c r="CC9" t="n">
+      <c r="CC9">
         <v>85.98</v>
       </c>
-      <c r="CD9" t="n">
-        <v>0.0</v>
+      <c r="CD9">
+        <v>0</v>
       </c>
       <c r="CE9" t="s">
         <v>120</v>
@@ -3266,8 +3535,8 @@
       <c r="CQ9" t="s">
         <v>141</v>
       </c>
-      <c r="CT9" t="n">
-        <v>0.0</v>
+      <c r="CT9">
+        <v>0</v>
       </c>
       <c r="CZ9" t="s">
         <v>126</v>
@@ -3276,7 +3545,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>161</v>
       </c>
@@ -3337,56 +3606,56 @@
       <c r="BJ10" t="s">
         <v>119</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN10" t="n">
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
         <v>561.6</v>
       </c>
-      <c r="BO10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
         <v>1428.96</v>
       </c>
-      <c r="BR10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>84.567</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>75.567</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0.0</v>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>16705</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10">
+        <v>84.566999999999993</v>
+      </c>
+      <c r="CC10">
+        <v>75.566999999999993</v>
+      </c>
+      <c r="CD10">
+        <v>0</v>
       </c>
       <c r="CE10" t="s">
         <v>120</v>
@@ -3415,8 +3684,8 @@
       <c r="CQ10" t="s">
         <v>141</v>
       </c>
-      <c r="CT10" t="n">
-        <v>0.0</v>
+      <c r="CT10">
+        <v>0</v>
       </c>
       <c r="CZ10" t="s">
         <v>126</v>
@@ -3425,7 +3694,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -3489,56 +3758,56 @@
       <c r="BJ11" t="s">
         <v>119</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BK11">
         <v>0.04</v>
       </c>
-      <c r="BL11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO11" t="n">
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
         <v>0.04</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BP11">
         <v>2.41</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU11" t="n">
+      <c r="BQ11">
+        <v>20</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
         <v>22.45</v>
       </c>
-      <c r="BV11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB11" t="n">
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>16705</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11">
         <v>3.2</v>
       </c>
-      <c r="CC11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>0.038</v>
+      <c r="CC11">
+        <v>3</v>
+      </c>
+      <c r="CD11">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE11" t="s">
         <v>120</v>
@@ -3567,11 +3836,11 @@
       <c r="CQ11" t="s">
         <v>141</v>
       </c>
-      <c r="CT11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>0.0</v>
+      <c r="CT11">
+        <v>0</v>
+      </c>
+      <c r="CV11">
+        <v>0</v>
       </c>
       <c r="CZ11" t="s">
         <v>126</v>
@@ -3580,7 +3849,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -3656,56 +3925,56 @@
       <c r="BJ12" t="s">
         <v>119</v>
       </c>
-      <c r="BK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP12" t="n">
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
         <v>0.17</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CC12" t="n">
+      <c r="BQ12">
+        <v>2</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>16705</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12">
+        <v>2</v>
+      </c>
+      <c r="CC12">
         <v>1.8</v>
       </c>
-      <c r="CD12" t="n">
-        <v>0.038</v>
+      <c r="CD12">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE12" t="s">
         <v>120</v>
@@ -3734,11 +4003,11 @@
       <c r="CQ12" t="s">
         <v>141</v>
       </c>
-      <c r="CT12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>0.0</v>
+      <c r="CT12">
+        <v>0</v>
+      </c>
+      <c r="CV12">
+        <v>0</v>
       </c>
       <c r="CZ12" t="s">
         <v>126</v>
@@ -3748,30 +4017,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3786,29 +4051,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3820,28 +4081,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3856,32 +4113,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3905,56 +4158,51 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:AO1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4080,50 +4328,46 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4201,32 +4445,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4247,31 +4487,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4289,36 +4525,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4351,28 +4583,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4386,11 +4614,11 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -4400,11 +4628,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -4414,11 +4642,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -4428,11 +4656,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -4442,11 +4670,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -4456,11 +4684,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -4470,11 +4698,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>157</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -4484,11 +4712,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -4498,11 +4726,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>161</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -4512,11 +4740,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>165</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -4526,11 +4754,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -4541,41 +4769,37 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:P62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="51.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="171.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="171.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4625,7 +4849,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -4657,7 +4881,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -4686,7 +4910,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -4706,7 +4930,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -4726,7 +4950,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -4749,7 +4973,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -4769,7 +4993,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -4801,7 +5025,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -4830,7 +5054,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>127</v>
       </c>
@@ -4841,7 +5065,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -4864,7 +5088,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -4884,7 +5108,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -4904,7 +5128,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -4936,7 +5160,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>137</v>
       </c>
@@ -4965,7 +5189,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>137</v>
       </c>
@@ -4985,7 +5209,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>137</v>
       </c>
@@ -5008,7 +5232,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -5040,7 +5264,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>143</v>
       </c>
@@ -5060,7 +5284,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>143</v>
       </c>
@@ -5089,7 +5313,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>143</v>
       </c>
@@ -5100,7 +5324,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -5123,7 +5347,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>143</v>
       </c>
@@ -5143,7 +5367,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -5166,7 +5390,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>148</v>
       </c>
@@ -5186,7 +5410,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>148</v>
       </c>
@@ -5197,7 +5421,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>148</v>
       </c>
@@ -5226,7 +5450,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>148</v>
       </c>
@@ -5246,7 +5470,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -5278,7 +5502,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>152</v>
       </c>
@@ -5301,7 +5525,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>152</v>
       </c>
@@ -5312,7 +5536,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -5323,7 +5547,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>152</v>
       </c>
@@ -5352,7 +5576,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>152</v>
       </c>
@@ -5372,7 +5596,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>152</v>
       </c>
@@ -5392,7 +5616,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -5424,7 +5648,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>157</v>
       </c>
@@ -5453,7 +5677,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -5473,7 +5697,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>157</v>
       </c>
@@ -5493,7 +5717,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>157</v>
       </c>
@@ -5516,7 +5740,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -5548,7 +5772,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>159</v>
       </c>
@@ -5577,7 +5801,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -5597,7 +5821,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>159</v>
       </c>
@@ -5617,7 +5841,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>159</v>
       </c>
@@ -5640,7 +5864,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>161</v>
       </c>
@@ -5660,7 +5884,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>161</v>
       </c>
@@ -5692,7 +5916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>161</v>
       </c>
@@ -5721,7 +5945,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>161</v>
       </c>
@@ -5741,7 +5965,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>161</v>
       </c>
@@ -5764,7 +5988,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>165</v>
       </c>
@@ -5793,7 +6017,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>165</v>
       </c>
@@ -5816,7 +6040,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>165</v>
       </c>
@@ -5836,7 +6060,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>165</v>
       </c>
@@ -5847,7 +6071,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>165</v>
       </c>
@@ -5867,7 +6091,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -5899,7 +6123,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -5919,7 +6143,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>168</v>
       </c>
@@ -5951,7 +6175,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>168</v>
       </c>
@@ -5980,7 +6204,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>168</v>
       </c>
@@ -5991,7 +6215,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>168</v>
       </c>
@@ -6014,7 +6238,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>168</v>
       </c>
@@ -6035,58 +6259,50 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>476</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6100,7 +6316,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -6114,7 +6330,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>143</v>
       </c>
@@ -6128,7 +6344,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -6142,7 +6358,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -6156,7 +6372,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -6170,7 +6386,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>165</v>
       </c>
@@ -6184,7 +6400,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>165</v>
       </c>
@@ -6195,7 +6411,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
@@ -6209,7 +6425,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -6223,7 +6439,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -6234,7 +6450,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -6248,7 +6464,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -6262,7 +6478,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -6277,32 +6493,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6325,12 +6537,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
-        <v>1.0</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>261</v>
@@ -6342,12 +6554,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
-        <v>2.0</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>264</v>
@@ -6359,12 +6571,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.0</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>266</v>
@@ -6376,12 +6588,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
-      <c r="B5" t="n">
-        <v>4.0</v>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>192</v>
@@ -6393,12 +6605,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>104</v>
       </c>
-      <c r="B6" t="n">
-        <v>5.0</v>
+      <c r="B6">
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>192</v>
@@ -6410,12 +6622,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
-      <c r="B7" t="n">
-        <v>6.0</v>
+      <c r="B7">
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>192</v>
@@ -6427,12 +6639,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>127</v>
       </c>
-      <c r="B8" t="n">
-        <v>1.0</v>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>261</v>
@@ -6444,12 +6656,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
-      <c r="B9" t="n">
-        <v>2.0</v>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>264</v>
@@ -6461,12 +6673,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>127</v>
       </c>
-      <c r="B10" t="n">
-        <v>3.0</v>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10" t="s">
         <v>266</v>
@@ -6478,12 +6690,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>127</v>
       </c>
-      <c r="B11" t="n">
-        <v>4.0</v>
+      <c r="B11">
+        <v>4</v>
       </c>
       <c r="C11" t="s">
         <v>275</v>
@@ -6495,12 +6707,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>137</v>
       </c>
-      <c r="B12" t="n">
-        <v>1.0</v>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>261</v>
@@ -6512,12 +6724,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="n">
-        <v>2.0</v>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="s">
         <v>264</v>
@@ -6529,12 +6741,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
-      <c r="B14" t="n">
-        <v>3.0</v>
+      <c r="B14">
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>266</v>
@@ -6546,12 +6758,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>137</v>
       </c>
-      <c r="B15" t="n">
-        <v>4.0</v>
+      <c r="B15">
+        <v>4</v>
       </c>
       <c r="C15" t="s">
         <v>192</v>
@@ -6563,12 +6775,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>143</v>
       </c>
-      <c r="B16" t="n">
-        <v>1.0</v>
+      <c r="B16">
+        <v>1</v>
       </c>
       <c r="C16" t="s">
         <v>261</v>
@@ -6580,12 +6792,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>143</v>
       </c>
-      <c r="B17" t="n">
-        <v>2.0</v>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="s">
         <v>264</v>
@@ -6597,12 +6809,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>143</v>
       </c>
-      <c r="B18" t="n">
-        <v>3.0</v>
+      <c r="B18">
+        <v>3</v>
       </c>
       <c r="C18" t="s">
         <v>266</v>
@@ -6614,12 +6826,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>143</v>
       </c>
-      <c r="B19" t="n">
-        <v>4.0</v>
+      <c r="B19">
+        <v>4</v>
       </c>
       <c r="C19" t="s">
         <v>275</v>
@@ -6631,12 +6843,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>148</v>
       </c>
-      <c r="B20" t="n">
-        <v>1.0</v>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>261</v>
@@ -6648,12 +6860,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>148</v>
       </c>
-      <c r="B21" t="n">
-        <v>2.0</v>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>264</v>
@@ -6665,12 +6877,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>148</v>
       </c>
-      <c r="B22" t="n">
-        <v>3.0</v>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>266</v>
@@ -6682,12 +6894,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>148</v>
       </c>
-      <c r="B23" t="n">
-        <v>4.0</v>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>275</v>
@@ -6699,12 +6911,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>152</v>
       </c>
-      <c r="B24" t="n">
-        <v>1.0</v>
+      <c r="B24">
+        <v>1</v>
       </c>
       <c r="C24" t="s">
         <v>261</v>
@@ -6716,12 +6928,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>152</v>
       </c>
-      <c r="B25" t="n">
-        <v>2.0</v>
+      <c r="B25">
+        <v>2</v>
       </c>
       <c r="C25" t="s">
         <v>264</v>
@@ -6733,12 +6945,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>152</v>
       </c>
-      <c r="B26" t="n">
-        <v>3.0</v>
+      <c r="B26">
+        <v>3</v>
       </c>
       <c r="C26" t="s">
         <v>266</v>
@@ -6750,12 +6962,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>152</v>
       </c>
-      <c r="B27" t="n">
-        <v>4.0</v>
+      <c r="B27">
+        <v>4</v>
       </c>
       <c r="C27" t="s">
         <v>192</v>
@@ -6767,12 +6979,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>152</v>
       </c>
-      <c r="B28" t="n">
-        <v>7.0</v>
+      <c r="B28">
+        <v>7</v>
       </c>
       <c r="C28" t="s">
         <v>192</v>
@@ -6784,12 +6996,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>152</v>
       </c>
-      <c r="B29" t="n">
-        <v>8.0</v>
+      <c r="B29">
+        <v>8</v>
       </c>
       <c r="C29" t="s">
         <v>192</v>
@@ -6801,12 +7013,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>152</v>
       </c>
-      <c r="B30" t="n">
-        <v>6.0</v>
+      <c r="B30">
+        <v>6</v>
       </c>
       <c r="C30" t="s">
         <v>192</v>
@@ -6818,12 +7030,12 @@
         <v>292</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>152</v>
       </c>
-      <c r="B31" t="n">
-        <v>5.0</v>
+      <c r="B31">
+        <v>5</v>
       </c>
       <c r="C31" t="s">
         <v>192</v>
@@ -6835,12 +7047,12 @@
         <v>294</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>157</v>
       </c>
-      <c r="B32" t="n">
-        <v>1.0</v>
+      <c r="B32">
+        <v>1</v>
       </c>
       <c r="C32" t="s">
         <v>261</v>
@@ -6852,12 +7064,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>157</v>
       </c>
-      <c r="B33" t="n">
-        <v>2.0</v>
+      <c r="B33">
+        <v>2</v>
       </c>
       <c r="C33" t="s">
         <v>264</v>
@@ -6869,12 +7081,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>157</v>
       </c>
-      <c r="B34" t="n">
-        <v>3.0</v>
+      <c r="B34">
+        <v>3</v>
       </c>
       <c r="C34" t="s">
         <v>266</v>
@@ -6886,12 +7098,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>157</v>
       </c>
-      <c r="B35" t="n">
-        <v>4.0</v>
+      <c r="B35">
+        <v>4</v>
       </c>
       <c r="C35" t="s">
         <v>192</v>
@@ -6903,12 +7115,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>159</v>
       </c>
-      <c r="B36" t="n">
-        <v>1.0</v>
+      <c r="B36">
+        <v>1</v>
       </c>
       <c r="C36" t="s">
         <v>261</v>
@@ -6920,12 +7132,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>159</v>
       </c>
-      <c r="B37" t="n">
-        <v>2.0</v>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="s">
         <v>264</v>
@@ -6937,12 +7149,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>159</v>
       </c>
-      <c r="B38" t="n">
-        <v>3.0</v>
+      <c r="B38">
+        <v>3</v>
       </c>
       <c r="C38" t="s">
         <v>266</v>
@@ -6954,12 +7166,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>159</v>
       </c>
-      <c r="B39" t="n">
-        <v>4.0</v>
+      <c r="B39">
+        <v>4</v>
       </c>
       <c r="C39" t="s">
         <v>192</v>
@@ -6971,12 +7183,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>161</v>
       </c>
-      <c r="B40" t="n">
-        <v>1.0</v>
+      <c r="B40">
+        <v>1</v>
       </c>
       <c r="C40" t="s">
         <v>261</v>
@@ -6988,12 +7200,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>161</v>
       </c>
-      <c r="B41" t="n">
-        <v>2.0</v>
+      <c r="B41">
+        <v>2</v>
       </c>
       <c r="C41" t="s">
         <v>264</v>
@@ -7005,12 +7217,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>161</v>
       </c>
-      <c r="B42" t="n">
-        <v>3.0</v>
+      <c r="B42">
+        <v>3</v>
       </c>
       <c r="C42" t="s">
         <v>266</v>
@@ -7022,12 +7234,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>161</v>
       </c>
-      <c r="B43" t="n">
-        <v>4.0</v>
+      <c r="B43">
+        <v>4</v>
       </c>
       <c r="C43" t="s">
         <v>192</v>
@@ -7039,12 +7251,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>161</v>
       </c>
-      <c r="B44" t="n">
-        <v>5.0</v>
+      <c r="B44">
+        <v>5</v>
       </c>
       <c r="C44" t="s">
         <v>192</v>
@@ -7056,12 +7268,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>161</v>
       </c>
-      <c r="B45" t="n">
-        <v>6.0</v>
+      <c r="B45">
+        <v>6</v>
       </c>
       <c r="C45" t="s">
         <v>192</v>
@@ -7073,12 +7285,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>165</v>
       </c>
-      <c r="B46" t="n">
-        <v>1.0</v>
+      <c r="B46">
+        <v>1</v>
       </c>
       <c r="C46" t="s">
         <v>261</v>
@@ -7090,12 +7302,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>165</v>
       </c>
-      <c r="B47" t="n">
-        <v>2.0</v>
+      <c r="B47">
+        <v>2</v>
       </c>
       <c r="C47" t="s">
         <v>264</v>
@@ -7107,12 +7319,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>165</v>
       </c>
-      <c r="B48" t="n">
-        <v>3.0</v>
+      <c r="B48">
+        <v>3</v>
       </c>
       <c r="C48" t="s">
         <v>266</v>
@@ -7124,12 +7336,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>165</v>
       </c>
-      <c r="B49" t="n">
-        <v>4.0</v>
+      <c r="B49">
+        <v>4</v>
       </c>
       <c r="C49" t="s">
         <v>275</v>
@@ -7141,12 +7353,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>168</v>
       </c>
-      <c r="B50" t="n">
-        <v>1.0</v>
+      <c r="B50">
+        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>261</v>
@@ -7158,12 +7370,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>168</v>
       </c>
-      <c r="B51" t="n">
-        <v>2.0</v>
+      <c r="B51">
+        <v>2</v>
       </c>
       <c r="C51" t="s">
         <v>264</v>
@@ -7175,12 +7387,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>168</v>
       </c>
-      <c r="B52" t="n">
-        <v>3.0</v>
+      <c r="B52">
+        <v>3</v>
       </c>
       <c r="C52" t="s">
         <v>266</v>
@@ -7192,12 +7404,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>168</v>
       </c>
-      <c r="B53" t="n">
-        <v>4.0</v>
+      <c r="B53">
+        <v>4</v>
       </c>
       <c r="C53" t="s">
         <v>275</v>
@@ -7210,34 +7422,30 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7266,11 +7474,11 @@
         <v>308</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -7286,11 +7494,11 @@
         <v>311</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -7306,11 +7514,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -7326,11 +7534,11 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -7346,11 +7554,11 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -7366,11 +7574,11 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -7386,11 +7594,11 @@
         <v>322</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>157</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -7406,11 +7614,11 @@
         <v>208</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -7426,11 +7634,11 @@
         <v>208</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>161</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -7446,11 +7654,11 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>165</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -7466,11 +7674,11 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -7487,30 +7695,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7527,184 +7731,184 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>330</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>332</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>330</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>332</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>332</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>330</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>465</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>157</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>330</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>24</v>
       </c>
       <c r="E8" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>330</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>11</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>161</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>330</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>11</v>
       </c>
       <c r="E10" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>165</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>333</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>332</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
@@ -7712,31 +7916,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7756,11 +7956,11 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>152</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -7777,40 +7977,34 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7873,87 +8067,83 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:BR15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="150.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="150.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+    <col min="20" max="22" width="9.140625" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" customWidth="1"/>
+    <col min="29" max="29" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.42578125" customWidth="1"/>
+    <col min="31" max="31" width="9.140625" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" customWidth="1"/>
+    <col min="33" max="33" width="9.140625" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" customWidth="1"/>
+    <col min="36" max="36" width="22.7109375" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:70" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8165,11 +8355,11 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -8196,53 +8386,53 @@
       <c r="J2" t="s">
         <v>396</v>
       </c>
-      <c r="K2" t="n">
-        <v>600.0</v>
+      <c r="K2">
+        <v>600</v>
       </c>
       <c r="L2" t="s">
         <v>330</v>
       </c>
-      <c r="M2" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>69.425</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1380.0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
+      <c r="M2">
+        <v>11</v>
+      </c>
+      <c r="T2">
+        <v>69.424999999999997</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>16738</v>
+      </c>
+      <c r="AC2">
+        <v>1380</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
       </c>
       <c r="AS2" t="s">
         <v>397</v>
@@ -8250,8 +8440,8 @@
       <c r="AY2" t="s">
         <v>398</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
+      <c r="BJ2">
+        <v>0</v>
       </c>
       <c r="BO2" t="s">
         <v>108</v>
@@ -8260,11 +8450,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -8291,56 +8481,56 @@
       <c r="J3" t="s">
         <v>396</v>
       </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
+      <c r="K3">
+        <v>20</v>
       </c>
       <c r="L3" t="s">
         <v>332</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>16705</v>
+      </c>
+      <c r="AC3">
+        <v>4</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>0.2</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
       </c>
       <c r="AS3" t="s">
         <v>397</v>
@@ -8348,8 +8538,8 @@
       <c r="AY3" t="s">
         <v>398</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="BJ3">
+        <v>0</v>
       </c>
       <c r="BO3" t="s">
         <v>108</v>
@@ -8358,11 +8548,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -8389,53 +8579,53 @@
       <c r="J4" t="s">
         <v>396</v>
       </c>
-      <c r="K4" t="n">
-        <v>310.0</v>
+      <c r="K4">
+        <v>310</v>
       </c>
       <c r="L4" t="s">
         <v>330</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="T4">
         <v>25.81</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>613.8</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>16705</v>
+      </c>
+      <c r="AC4">
+        <v>613.79999999999995</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
         <v>1.98</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
       </c>
       <c r="AS4" t="s">
         <v>397</v>
@@ -8443,8 +8633,8 @@
       <c r="AY4" t="s">
         <v>398</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
+      <c r="BJ4">
+        <v>0</v>
       </c>
       <c r="BO4" t="s">
         <v>108</v>
@@ -8453,11 +8643,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -8484,56 +8674,56 @@
       <c r="J5" t="s">
         <v>396</v>
       </c>
-      <c r="K5" t="n">
-        <v>6.0</v>
+      <c r="K5">
+        <v>6</v>
       </c>
       <c r="L5" t="s">
         <v>332</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>16705</v>
+      </c>
+      <c r="AC5">
+        <v>6</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
       </c>
       <c r="AS5" t="s">
         <v>397</v>
@@ -8541,8 +8731,8 @@
       <c r="AY5" t="s">
         <v>398</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
+      <c r="BJ5">
+        <v>0</v>
       </c>
       <c r="BO5" t="s">
         <v>108</v>
@@ -8551,11 +8741,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -8582,56 +8772,56 @@
       <c r="J6" t="s">
         <v>396</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.0</v>
+      <c r="K6">
+        <v>4</v>
       </c>
       <c r="L6" t="s">
         <v>332</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>16705</v>
+      </c>
+      <c r="AC6">
+        <v>4</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
       </c>
       <c r="AS6" t="s">
         <v>397</v>
@@ -8639,8 +8829,8 @@
       <c r="AY6" t="s">
         <v>398</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
+      <c r="BJ6">
+        <v>0</v>
       </c>
       <c r="BO6" t="s">
         <v>108</v>
@@ -8649,11 +8839,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -8680,56 +8870,57 @@
       <c r="J7" t="s">
         <v>412</v>
       </c>
-      <c r="K7" t="n">
-        <v>13470.0</v>
+      <c r="K7">
+        <v>13470</v>
       </c>
       <c r="L7" t="s">
         <v>330</v>
       </c>
-      <c r="M7" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="M7">
+        <v>277</v>
+      </c>
+      <c r="T7">
         <v>3957.88</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>0.52</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>16705</v>
+      </c>
+      <c r="AC7">
+        <f>AJ7*K7</f>
         <v>98721.63</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0</v>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>7.3290000000000006</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
       </c>
       <c r="AS7" t="s">
         <v>397</v>
@@ -8737,8 +8928,8 @@
       <c r="AY7" t="s">
         <v>398</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>0.0</v>
+      <c r="BJ7">
+        <v>0</v>
       </c>
       <c r="BO7" t="s">
         <v>108</v>
@@ -8747,11 +8938,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>152</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
@@ -8778,56 +8969,57 @@
       <c r="J8" t="s">
         <v>396</v>
       </c>
-      <c r="K8" t="n">
-        <v>553.0</v>
+      <c r="K8">
+        <v>553</v>
       </c>
       <c r="L8" t="s">
         <v>330</v>
       </c>
-      <c r="M8" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="M8">
+        <v>8</v>
+      </c>
+      <c r="T8">
         <v>99.31</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>0.52</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>16705</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" ref="AC8:AC10" si="0">AJ8*K8</f>
         <v>1871.91</v>
       </c>
-      <c r="AF8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0</v>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>3.3850090415913203</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
       </c>
       <c r="AS8" t="s">
         <v>397</v>
@@ -8835,8 +9027,8 @@
       <c r="AY8" t="s">
         <v>398</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
+      <c r="BJ8">
+        <v>0</v>
       </c>
       <c r="BO8" t="s">
         <v>108</v>
@@ -8845,11 +9037,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>152</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
@@ -8876,56 +9068,57 @@
       <c r="J9" t="s">
         <v>396</v>
       </c>
-      <c r="K9" t="n">
-        <v>6342.0</v>
+      <c r="K9">
+        <v>6342</v>
       </c>
       <c r="L9" t="s">
         <v>330</v>
       </c>
-      <c r="M9" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1151.13</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="M9">
+        <v>93</v>
+      </c>
+      <c r="T9">
+        <v>1151.1300000000001</v>
+      </c>
+      <c r="V9">
         <v>0.52</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>16705</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="0"/>
         <v>21588.17</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0</v>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>3.4040003153579308</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
       </c>
       <c r="AS9" t="s">
         <v>397</v>
@@ -8933,8 +9126,8 @@
       <c r="AY9" t="s">
         <v>398</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0.0</v>
+      <c r="BJ9">
+        <v>0</v>
       </c>
       <c r="BO9" t="s">
         <v>108</v>
@@ -8943,11 +9136,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>152</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
@@ -8974,56 +9167,57 @@
       <c r="J10" t="s">
         <v>396</v>
       </c>
-      <c r="K10" t="n">
-        <v>5908.0</v>
+      <c r="K10">
+        <v>5908</v>
       </c>
       <c r="L10" t="s">
         <v>330</v>
       </c>
-      <c r="M10" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="M10">
+        <v>87</v>
+      </c>
+      <c r="T10">
         <v>1077.94</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10">
         <v>0.52</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>20110.83</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0</v>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>16705</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="0"/>
+        <v>20110.830000000002</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>3.4039996614759649</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
       </c>
       <c r="AS10" t="s">
         <v>397</v>
@@ -9031,8 +9225,8 @@
       <c r="AY10" t="s">
         <v>398</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>0.0</v>
+      <c r="BJ10">
+        <v>0</v>
       </c>
       <c r="BO10" t="s">
         <v>108</v>
@@ -9041,11 +9235,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>157</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -9072,53 +9266,53 @@
       <c r="J11" t="s">
         <v>396</v>
       </c>
-      <c r="K11" t="n">
-        <v>3465.0</v>
+      <c r="K11">
+        <v>3465</v>
       </c>
       <c r="L11" t="s">
         <v>330</v>
       </c>
-      <c r="M11" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="M11">
+        <v>24</v>
+      </c>
+      <c r="T11">
         <v>278.31</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>16705</v>
+      </c>
+      <c r="AC11">
         <v>7033.95</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.0</v>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
       </c>
       <c r="AS11" t="s">
         <v>397</v>
@@ -9126,8 +9320,8 @@
       <c r="AY11" t="s">
         <v>398</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>0.0</v>
+      <c r="BJ11">
+        <v>0</v>
       </c>
       <c r="BO11" t="s">
         <v>108</v>
@@ -9136,11 +9330,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>159</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -9167,53 +9361,53 @@
       <c r="J12" t="s">
         <v>396</v>
       </c>
-      <c r="K12" t="n">
-        <v>1032.0</v>
+      <c r="K12">
+        <v>1032</v>
       </c>
       <c r="L12" t="s">
         <v>330</v>
       </c>
-      <c r="M12" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="M12">
+        <v>11</v>
+      </c>
+      <c r="T12">
         <v>85.98</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>16705</v>
+      </c>
+      <c r="AC12">
         <v>2043.36</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>1.98</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.0</v>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
       </c>
       <c r="AS12" t="s">
         <v>397</v>
@@ -9221,8 +9415,8 @@
       <c r="AY12" t="s">
         <v>398</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>0.0</v>
+      <c r="BJ12">
+        <v>0</v>
       </c>
       <c r="BO12" t="s">
         <v>108</v>
@@ -9231,11 +9425,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>161</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
@@ -9262,53 +9456,53 @@
       <c r="J13" t="s">
         <v>396</v>
       </c>
-      <c r="K13" t="n">
-        <v>624.0</v>
+      <c r="K13">
+        <v>624</v>
       </c>
       <c r="L13" t="s">
         <v>330</v>
       </c>
-      <c r="M13" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>75.567</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="M13">
+        <v>11</v>
+      </c>
+      <c r="T13">
+        <v>75.566999999999993</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>16705</v>
+      </c>
+      <c r="AC13">
         <v>1428.96</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
         <v>2.29</v>
       </c>
-      <c r="AK13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.0</v>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
       </c>
       <c r="AS13" t="s">
         <v>397</v>
@@ -9316,8 +9510,8 @@
       <c r="AY13" t="s">
         <v>398</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>0.0</v>
+      <c r="BJ13">
+        <v>0</v>
       </c>
       <c r="BO13" t="s">
         <v>108</v>
@@ -9326,11 +9520,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>165</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
@@ -9357,56 +9551,56 @@
       <c r="J14" t="s">
         <v>396</v>
       </c>
-      <c r="K14" t="n">
-        <v>20.0</v>
+      <c r="K14">
+        <v>20</v>
       </c>
       <c r="L14" t="s">
         <v>333</v>
       </c>
-      <c r="M14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.0</v>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>3</v>
+      </c>
+      <c r="V14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>16705</v>
+      </c>
+      <c r="AC14">
+        <v>20</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
       </c>
       <c r="AS14" t="s">
         <v>397</v>
@@ -9414,8 +9608,8 @@
       <c r="AY14" t="s">
         <v>398</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>0.0</v>
+      <c r="BJ14">
+        <v>0</v>
       </c>
       <c r="BO14" t="s">
         <v>108</v>
@@ -9424,11 +9618,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>168</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -9455,56 +9649,56 @@
       <c r="J15" t="s">
         <v>396</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.0</v>
+      <c r="K15">
+        <v>4</v>
       </c>
       <c r="L15" t="s">
         <v>332</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="T15">
         <v>1.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16705.0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="V15">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>16705</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
         <v>0.5</v>
       </c>
-      <c r="AK15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.0</v>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
       </c>
       <c r="AS15" t="s">
         <v>397</v>
@@ -9512,8 +9706,8 @@
       <c r="AY15" t="s">
         <v>398</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>0.0</v>
+      <c r="BJ15">
+        <v>0</v>
       </c>
       <c r="BO15" t="s">
         <v>108</v>
@@ -9523,44 +9717,40 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9620,11 +9810,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>